--- a/dataset_t6_grouped/results2/G2/G2_T2508_W0076F0002T0006Z000C1N20_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G2/G2_T2508_W0076F0002T0006Z000C1N20_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>97.68505007095442</v>
+        <v>15.87382063653009</v>
       </c>
       <c r="D2" t="n">
-        <v>98.64706459374199</v>
+        <v>16.03014799648307</v>
       </c>
       <c r="E2" t="n">
-        <v>26.37416478223301</v>
+        <v>4.285801777112866</v>
       </c>
       <c r="F2" t="n">
-        <v>26.73455581625808</v>
+        <v>4.344365320141939</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>91.55345343124526</v>
+        <v>14.87743618257736</v>
       </c>
       <c r="D3" t="n">
-        <v>92.44249020704625</v>
+        <v>15.02190465864502</v>
       </c>
       <c r="E3" t="n">
-        <v>26.37416478223301</v>
+        <v>4.285801777112866</v>
       </c>
       <c r="F3" t="n">
-        <v>26.73455581625808</v>
+        <v>4.344365320141939</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>85.69718364685529</v>
+        <v>13.92579234261399</v>
       </c>
       <c r="D4" t="n">
-        <v>86.57200341101112</v>
+        <v>14.06795055428931</v>
       </c>
       <c r="E4" t="n">
-        <v>26.37416478223301</v>
+        <v>4.285801777112866</v>
       </c>
       <c r="F4" t="n">
-        <v>26.73455581625808</v>
+        <v>4.344365320141939</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>98.75763147235554</v>
+        <v>16.04811511425778</v>
       </c>
       <c r="D5" t="n">
-        <v>99.79410920365795</v>
+        <v>16.21654274559442</v>
       </c>
       <c r="E5" t="n">
-        <v>26.37416478223301</v>
+        <v>4.285801777112866</v>
       </c>
       <c r="F5" t="n">
-        <v>26.73455581625808</v>
+        <v>4.344365320141939</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>70.82274830328778</v>
+        <v>11.50869659928427</v>
       </c>
       <c r="D6" t="n">
-        <v>71.73679407495926</v>
+        <v>11.65722903718088</v>
       </c>
       <c r="E6" t="n">
-        <v>26.37416478223301</v>
+        <v>4.285801777112866</v>
       </c>
       <c r="F6" t="n">
-        <v>26.73455581625808</v>
+        <v>4.344365320141939</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>36.72240509016103</v>
+        <v>5.967390827151167</v>
       </c>
       <c r="D7" t="n">
-        <v>36.8565264375092</v>
+        <v>5.989185546095245</v>
       </c>
       <c r="E7" t="n">
-        <v>26.37416478223301</v>
+        <v>4.285801777112866</v>
       </c>
       <c r="F7" t="n">
-        <v>26.73455581625808</v>
+        <v>4.344365320141939</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>39.4457932701276</v>
+        <v>6.409941406395735</v>
       </c>
       <c r="D8" t="n">
-        <v>39.15013349205445</v>
+        <v>6.361896692458848</v>
       </c>
       <c r="E8" t="n">
-        <v>26.37416478223301</v>
+        <v>4.285801777112866</v>
       </c>
       <c r="F8" t="n">
-        <v>26.73455581625808</v>
+        <v>4.344365320141939</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>30.89481006766595</v>
+        <v>5.020406635995717</v>
       </c>
       <c r="D9" t="n">
-        <v>31.36403951383671</v>
+        <v>5.096656420998465</v>
       </c>
       <c r="E9" t="n">
-        <v>26.37416478223301</v>
+        <v>4.285801777112866</v>
       </c>
       <c r="F9" t="n">
-        <v>26.73455581625808</v>
+        <v>4.344365320141939</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>39.86802236777032</v>
+        <v>6.478553634762677</v>
       </c>
       <c r="D10" t="n">
-        <v>38.91616847307826</v>
+        <v>6.323877376875217</v>
       </c>
       <c r="E10" t="n">
-        <v>26.37416478223301</v>
+        <v>4.285801777112866</v>
       </c>
       <c r="F10" t="n">
-        <v>26.73455581625808</v>
+        <v>4.344365320141939</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>58.25209152634763</v>
+        <v>9.46596487303149</v>
       </c>
       <c r="D11" t="n">
-        <v>59.51428768059446</v>
+        <v>9.671071748096601</v>
       </c>
       <c r="E11" t="n">
-        <v>26.37416478223301</v>
+        <v>4.285801777112866</v>
       </c>
       <c r="F11" t="n">
-        <v>26.73455581625808</v>
+        <v>4.344365320141939</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>71.40520332352929</v>
+        <v>11.60334554007351</v>
       </c>
       <c r="D12" t="n">
-        <v>72.68253138562132</v>
+        <v>11.81091135016347</v>
       </c>
       <c r="E12" t="n">
-        <v>26.37416478223301</v>
+        <v>4.285801777112866</v>
       </c>
       <c r="F12" t="n">
-        <v>26.73455581625808</v>
+        <v>4.344365320141939</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>15.66803897616636</v>
+        <v>2.546056333627034</v>
       </c>
       <c r="D13" t="n">
-        <v>16.70760026080493</v>
+        <v>2.714985042380802</v>
       </c>
       <c r="E13" t="n">
-        <v>26.37416478223301</v>
+        <v>4.285801777112866</v>
       </c>
       <c r="F13" t="n">
-        <v>26.73455581625808</v>
+        <v>4.344365320141939</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>21.67114928602014</v>
+        <v>3.521561758978273</v>
       </c>
       <c r="D14" t="n">
-        <v>22.94769782292163</v>
+        <v>3.729000896224764</v>
       </c>
       <c r="E14" t="n">
-        <v>26.37416478223301</v>
+        <v>4.285801777112866</v>
       </c>
       <c r="F14" t="n">
-        <v>26.73455581625808</v>
+        <v>4.344365320141939</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>4.497650159597775</v>
+        <v>0.7308681509346385</v>
       </c>
       <c r="D15" t="n">
-        <v>3.22315808728421</v>
+        <v>0.5237631891836841</v>
       </c>
       <c r="E15" t="n">
-        <v>26.37416478223301</v>
+        <v>4.285801777112866</v>
       </c>
       <c r="F15" t="n">
-        <v>26.73455581625808</v>
+        <v>4.344365320141939</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -928,16 +928,16 @@
         <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>42.93190489500967</v>
+        <v>6.976434545439071</v>
       </c>
       <c r="D16" t="n">
-        <v>41.68391579341596</v>
+        <v>6.773636316430094</v>
       </c>
       <c r="E16" t="n">
-        <v>26.37416478223301</v>
+        <v>4.285801777112866</v>
       </c>
       <c r="F16" t="n">
-        <v>26.73455581625808</v>
+        <v>4.344365320141939</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -960,16 +960,16 @@
         <v>16</v>
       </c>
       <c r="C17" t="n">
-        <v>53.31750996473378</v>
+        <v>8.664095369269239</v>
       </c>
       <c r="D17" t="n">
-        <v>52.04176198544104</v>
+        <v>8.456786322634169</v>
       </c>
       <c r="E17" t="n">
-        <v>26.37416478223301</v>
+        <v>4.285801777112866</v>
       </c>
       <c r="F17" t="n">
-        <v>26.73455581625808</v>
+        <v>4.344365320141939</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -992,16 +992,16 @@
         <v>17</v>
       </c>
       <c r="C18" t="n">
-        <v>17.20804074855436</v>
+        <v>2.796306621640084</v>
       </c>
       <c r="D18" t="n">
-        <v>16.38314784590618</v>
+        <v>2.662261524959754</v>
       </c>
       <c r="E18" t="n">
-        <v>26.37416478223301</v>
+        <v>4.285801777112866</v>
       </c>
       <c r="F18" t="n">
-        <v>26.73455581625808</v>
+        <v>4.344365320141939</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1024,16 +1024,16 @@
         <v>18</v>
       </c>
       <c r="C19" t="n">
-        <v>21.90551899668725</v>
+        <v>3.559646836961678</v>
       </c>
       <c r="D19" t="n">
-        <v>22.81069952974026</v>
+        <v>3.706738673582793</v>
       </c>
       <c r="E19" t="n">
-        <v>26.37416478223301</v>
+        <v>4.285801777112866</v>
       </c>
       <c r="F19" t="n">
-        <v>26.73455581625808</v>
+        <v>4.344365320141939</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1056,16 +1056,16 @@
         <v>19</v>
       </c>
       <c r="C20" t="n">
-        <v>19.30949129215215</v>
+        <v>3.137792334974725</v>
       </c>
       <c r="D20" t="n">
-        <v>18.7752176574001</v>
+        <v>3.050972869327517</v>
       </c>
       <c r="E20" t="n">
-        <v>26.37416478223301</v>
+        <v>4.285801777112866</v>
       </c>
       <c r="F20" t="n">
-        <v>26.73455581625808</v>
+        <v>4.344365320141939</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1088,16 +1088,16 @@
         <v>20</v>
       </c>
       <c r="C21" t="n">
-        <v>37.87779540491054</v>
+        <v>6.155141753297962</v>
       </c>
       <c r="D21" t="n">
-        <v>37.38803916147577</v>
+        <v>6.075556363739813</v>
       </c>
       <c r="E21" t="n">
-        <v>26.37416478223301</v>
+        <v>4.285801777112866</v>
       </c>
       <c r="F21" t="n">
-        <v>26.73455581625808</v>
+        <v>4.344365320141939</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -1120,16 +1120,16 @@
         <v>21</v>
       </c>
       <c r="C22" t="n">
-        <v>63.72758413086355</v>
+        <v>10.35573242126533</v>
       </c>
       <c r="D22" t="n">
-        <v>62.64802247772815</v>
+        <v>10.18030365263083</v>
       </c>
       <c r="E22" t="n">
-        <v>26.37416478223301</v>
+        <v>4.285801777112866</v>
       </c>
       <c r="F22" t="n">
-        <v>26.73455581625808</v>
+        <v>4.344365320141939</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -1152,16 +1152,16 @@
         <v>22</v>
       </c>
       <c r="C23" t="n">
-        <v>46.36301545682584</v>
+        <v>7.5339900117342</v>
       </c>
       <c r="D23" t="n">
-        <v>45.83135622177299</v>
+        <v>7.447595386038111</v>
       </c>
       <c r="E23" t="n">
-        <v>26.37416478223301</v>
+        <v>4.285801777112866</v>
       </c>
       <c r="F23" t="n">
-        <v>26.73455581625808</v>
+        <v>4.344365320141939</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -1184,16 +1184,16 @@
         <v>23</v>
       </c>
       <c r="C24" t="n">
-        <v>52.19544745579936</v>
+        <v>8.481760211567396</v>
       </c>
       <c r="D24" t="n">
-        <v>51.45913799149272</v>
+        <v>8.362109923617567</v>
       </c>
       <c r="E24" t="n">
-        <v>26.37416478223301</v>
+        <v>4.285801777112866</v>
       </c>
       <c r="F24" t="n">
-        <v>26.73455581625808</v>
+        <v>4.344365320141939</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -1216,16 +1216,16 @@
         <v>24</v>
       </c>
       <c r="C25" t="n">
-        <v>58.78837878438613</v>
+        <v>9.553111552462747</v>
       </c>
       <c r="D25" t="n">
-        <v>58.17432187063991</v>
+        <v>9.453327303978986</v>
       </c>
       <c r="E25" t="n">
-        <v>26.37416478223301</v>
+        <v>4.285801777112866</v>
       </c>
       <c r="F25" t="n">
-        <v>26.73455581625808</v>
+        <v>4.344365320141939</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
